--- a/public/TemplateExcel/Subject.xlsx
+++ b/public/TemplateExcel/Subject.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\buiho\OneDrive\Máy tính\TemplateExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAn\EduAttend\fe\public\TemplateExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3324899-F3D8-4AFC-B5C4-8C7DD584F577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5B083F-06E2-4320-8ABD-5F076873C71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,12 +68,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -362,18 +378,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
